--- a/ENTREGA_FINAL/RESULTADOS_ATUAIS/Modelo_A_Baseline_Oficial/04_Segundo_Turno_Lula_vs_Renan.xlsx
+++ b/ENTREGA_FINAL/RESULTADOS_ATUAIS/Modelo_A_Baseline_Oficial/04_Segundo_Turno_Lula_vs_Renan.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -586,6 +586,17 @@
       </c>
       <c r="C13" t="n">
         <v>37.28940911111843</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B14" t="n">
+        <v>60.82141531970473</v>
+      </c>
+      <c r="C14" t="n">
+        <v>39.17858468029527</v>
       </c>
     </row>
   </sheetData>
@@ -599,7 +610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -749,6 +760,17 @@
       </c>
       <c r="C13" t="n">
         <v>35.51950607434777</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B14" t="n">
+        <v>59.23759892250126</v>
+      </c>
+      <c r="C14" t="n">
+        <v>37.5947682830918</v>
       </c>
     </row>
   </sheetData>
@@ -762,7 +784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,6 +936,17 @@
         <v>39.0593121478891</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B14" t="n">
+        <v>62.4052317169082</v>
+      </c>
+      <c r="C14" t="n">
+        <v>40.76240107749874</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ENTREGA_FINAL/RESULTADOS_ATUAIS/Modelo_A_Baseline_Oficial/04_Segundo_Turno_Lula_vs_Renan.xlsx
+++ b/ENTREGA_FINAL/RESULTADOS_ATUAIS/Modelo_A_Baseline_Oficial/04_Segundo_Turno_Lula_vs_Renan.xlsx
@@ -10,8 +10,16 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Suavizados" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC_Baixo" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC_Alto" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cobertura" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metodologia" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Suavizados'!$A$1:$C$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'IC_Baixo'!$A$1:$C$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'IC_Alto'!$A$1:$C$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Cobertura'!$A$1:$B$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Metodologia'!$A$1:$B$6</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -22,7 +30,7 @@
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,16 +41,25 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -56,11 +73,16 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00A6A6A6"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -68,8 +90,17 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -436,170 +467,187 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>data</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Lula</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Renan</t>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Renan Santos</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>46140</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="6" t="n">
         <v>62.5</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="6" t="n">
         <v>37.49999999999999</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>46147</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="6" t="n">
         <v>62.77478741722351</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="6" t="n">
         <v>37.22521258277648</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>46154</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="6" t="n">
         <v>63.0377200834244</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="6" t="n">
         <v>36.9622799165756</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>46160</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="6" t="n">
         <v>62.9358043941657</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="6" t="n">
         <v>37.0641956058343</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>46167</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="6" t="n">
         <v>62.87417212077332</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="6" t="n">
         <v>37.12582787922669</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>46174</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" s="6" t="n">
         <v>62.90071837115898</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="6" t="n">
         <v>37.09928162884103</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>46181</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" s="6" t="n">
         <v>62.80163588111624</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="6" t="n">
         <v>37.19836411888375</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>46188</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" s="6" t="n">
         <v>62.8180372021143</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="6" t="n">
         <v>37.1819627978857</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>46195</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10" s="6" t="n">
         <v>62.78088684941638</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="6" t="n">
         <v>37.21911315058361</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>46202</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11" s="6" t="n">
         <v>63.09382210909057</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="6" t="n">
         <v>36.90617789090943</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>46209</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12" s="6" t="n">
         <v>62.72886730390231</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" s="6" t="n">
         <v>37.27113269609769</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>46216</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13" s="6" t="n">
         <v>62.71059088888158</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" s="6" t="n">
         <v>37.28940911111843</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>62.80917908143363</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>37.19082091856637</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n">
         <v>46224</v>
       </c>
-      <c r="B14" t="n">
-        <v>60.82141531970473</v>
-      </c>
-      <c r="C14" t="n">
-        <v>39.17858468029527</v>
+      <c r="B15" s="6" t="n">
+        <v>61.33206920174906</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>38.66793079825094</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -610,170 +658,187 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>data</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Lula</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Renan</t>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Renan Santos</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>46140</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="6" t="n">
         <v>58.62628104809649</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="6" t="n">
         <v>33.62628104809648</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>46147</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="6" t="n">
         <v>60.03838199500441</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="6" t="n">
         <v>34.48880716055738</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>46154</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="6" t="n">
         <v>60.80363120842867</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="6" t="n">
         <v>34.72819104157988</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>46160</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="6" t="n">
         <v>60.99388075847173</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="6" t="n">
         <v>35.12227197014033</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>46167</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="6" t="n">
         <v>61.11567180895585</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="6" t="n">
         <v>35.36732756740923</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>46174</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" s="6" t="n">
         <v>61.14224395224406</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="6" t="n">
         <v>35.3408072099261</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>46181</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" s="6" t="n">
         <v>61.04111702723365</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="6" t="n">
         <v>35.43784526500117</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>46188</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" s="6" t="n">
         <v>61.04962063303995</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="6" t="n">
         <v>35.41354622881134</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>46195</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10" s="6" t="n">
         <v>61.01192092511904</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="6" t="n">
         <v>35.45014722628626</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>46202</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11" s="6" t="n">
         <v>61.32847700019625</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="6" t="n">
         <v>35.1408327820151</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>46209</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12" s="6" t="n">
         <v>60.9593428386377</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" s="6" t="n">
         <v>35.50160823083309</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>46216</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13" s="6" t="n">
         <v>60.94068785211091</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" s="6" t="n">
         <v>35.51950607434777</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>61.04073905207034</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>35.42238088920307</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n">
         <v>46224</v>
       </c>
-      <c r="B14" t="n">
-        <v>59.23759892250126</v>
-      </c>
-      <c r="C14" t="n">
-        <v>37.5947682830918</v>
+      <c r="B15" s="6" t="n">
+        <v>59.8480716473514</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>37.18393324385328</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -784,170 +849,369 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>data</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Lula</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Renan</t>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Renan Santos</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>46140</v>
       </c>
+      <c r="B2" s="6" t="n">
+        <v>66.37371895190351</v>
+      </c>
+      <c r="C2" s="6" t="n">
+        <v>41.37371895190351</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B3" s="6" t="n">
+        <v>65.51119283944261</v>
+      </c>
+      <c r="C3" s="6" t="n">
+        <v>39.96161800499558</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>65.27180895842012</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>39.19636879157133</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>64.87772802985967</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>39.00611924152827</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="n">
+        <v>46167</v>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>64.63267243259078</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>38.88432819104415</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>64.6591927900739</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>38.85775604775595</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>64.56215473499883</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>38.95888297276634</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>64.58645377118866</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>38.95037936696005</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n">
+        <v>46195</v>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>64.54985277371374</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>38.98807907488096</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>64.8591672179849</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>38.67152299980375</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>64.49839176916693</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>39.0406571613623</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
+        <v>46216</v>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>64.48049392565224</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>39.0593121478891</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>64.57761911079693</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>38.95926094792966</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>62.81606675614671</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>40.15192835264859</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C15"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>indicador</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>observacoes_utilizadas</t>
+        </is>
+      </c>
       <c r="B2" t="n">
-        <v>66.37371895190351</v>
-      </c>
-      <c r="C2" t="n">
-        <v>41.37371895190351</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
-        <v>46147</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>datas_distintas</t>
+        </is>
       </c>
       <c r="B3" t="n">
-        <v>65.51119283944261</v>
-      </c>
-      <c r="C3" t="n">
-        <v>39.96161800499558</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
-        <v>46154</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>institutos_distintos</t>
+        </is>
       </c>
       <c r="B4" t="n">
-        <v>65.27180895842012</v>
-      </c>
-      <c r="C4" t="n">
-        <v>39.19636879157133</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
-        <v>46160</v>
-      </c>
-      <c r="B5" t="n">
-        <v>64.87772802985967</v>
-      </c>
-      <c r="C5" t="n">
-        <v>39.00611924152827</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>primeira_data</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>46140</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
-        <v>46167</v>
-      </c>
-      <c r="B6" t="n">
-        <v>64.63267243259078</v>
-      </c>
-      <c r="C6" t="n">
-        <v>38.88432819104415</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ultima_data</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n">
+        <v>46224</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
-        <v>46174</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>fallbacks_de_amostra</t>
+        </is>
       </c>
       <c r="B7" t="n">
-        <v>64.6591927900739</v>
-      </c>
-      <c r="C7" t="n">
-        <v>38.85775604775595</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="n">
-        <v>46181</v>
-      </c>
-      <c r="B8" t="n">
-        <v>64.56215473499883</v>
-      </c>
-      <c r="C8" t="n">
-        <v>38.95888297276634</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="n">
-        <v>46188</v>
-      </c>
-      <c r="B9" t="n">
-        <v>64.58645377118866</v>
-      </c>
-      <c r="C9" t="n">
-        <v>38.95037936696005</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="n">
-        <v>46195</v>
-      </c>
-      <c r="B10" t="n">
-        <v>64.54985277371374</v>
-      </c>
-      <c r="C10" t="n">
-        <v>38.98807907488096</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="n">
-        <v>46202</v>
-      </c>
-      <c r="B11" t="n">
-        <v>64.8591672179849</v>
-      </c>
-      <c r="C11" t="n">
-        <v>38.67152299980375</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="n">
-        <v>46209</v>
-      </c>
-      <c r="B12" t="n">
-        <v>64.49839176916693</v>
-      </c>
-      <c r="C12" t="n">
-        <v>39.0406571613623</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="n">
-        <v>46216</v>
-      </c>
-      <c r="B13" t="n">
-        <v>64.48049392565224</v>
-      </c>
-      <c r="C13" t="n">
-        <v>39.0593121478891</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="n">
-        <v>46224</v>
-      </c>
-      <c r="B14" t="n">
-        <v>62.4052317169082</v>
-      </c>
-      <c r="C14" t="n">
-        <v>40.76240107749874</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:B7"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>descricao</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Base dos percentuais</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>Votos válidos</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Denominador</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Reescala apenas Lula e o adversário para somarem 100%; brancos, nulos e indecisos saem do denominador.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Média ponderada</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Baseline legado em janela de 30 dias: qualidade do instituto, recência linear e tamanho de amostra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Faixa</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Faixa amostral aproximada de 1,96 erros-padrão; não incorpora heterogeneidade, efeito de instituto ou desenho amostral.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Interpretação</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Agregado de pesquisas para acompanhamento; não é previsão eleitoral nem probabilidade de vitória.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>